--- a/ig/DM-JUILLET-2026/CodeSystem-TRE-R243-CompetenceSpecifique.xlsx
+++ b/ig/DM-JUILLET-2026/CodeSystem-TRE-R243-CompetenceSpecifique.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -409,13 +409,13 @@
     <t>35</t>
   </si>
   <si>
-    <t>Maît des out info avc synthèse voc à entrée ortho ou picto (téléth, log de com)</t>
+    <t>Maîtrise des outils informatisés avec synthèse vocale à entrée orthographique ou pictographique (téléthèses, logiciels de communication)</t>
   </si>
   <si>
     <t>36</t>
   </si>
   <si>
-    <t>Maîtrise des log d'aide à la transcription (retour voc, prédicteur de mots)</t>
+    <t>Maîtrise des logiciels d'aide à la transcription (retour vocal, prédicteur de mots)</t>
   </si>
   <si>
     <t>37</t>

--- a/ig/DM-JUILLET-2026/CodeSystem-TRE-R243-CompetenceSpecifique.xlsx
+++ b/ig/DM-JUILLET-2026/CodeSystem-TRE-R243-CompetenceSpecifique.xlsx
@@ -439,7 +439,7 @@
     <t>40</t>
   </si>
   <si>
-    <t>Maîtrise de prog d'interv globaux à réf développementale (TEACCH, DENVER,...)</t>
+    <t>Maîtrise de programmes d'intervention globaux à référence développementale (TEACCH, DENVER,...)</t>
   </si>
   <si>
     <t>41</t>
